--- a/data/trans_orig/P37A$medicootras-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P37A$medicootras-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489312</t>
+          <t>490032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>956772</t>
+          <t>956769</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>730245</t>
+          <t>730575</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>617792</t>
+          <t>618429</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1351699</t>
+          <t>1352585</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1360002</t>
+          <t>1360005</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>959</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>681562</t>
+          <t>681721</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>688789</t>
+          <t>688784</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1319615</t>
+          <t>1320194</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1327458</t>
+          <t>1327453</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>918</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>10805</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1682</t>
+          <t>1692</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11918</t>
+          <t>12546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>508395</t>
+          <t>508342</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>518239</t>
+          <t>518229</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>510713</t>
+          <t>509799</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1022871</t>
+          <t>1022243</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1033107</t>
+          <t>1033097</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>398212</t>
+          <t>398872</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>785551</t>
+          <t>785018</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287212</t>
+          <t>286397</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>630136</t>
+          <t>629251</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>25425</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3262086</t>
+          <t>3261851</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3273636</t>
+          <t>3273564</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3364117</t>
+          <t>3364585</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3375962</t>
+          <t>3375959</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6630818</t>
+          <t>6630316</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6647089</t>
+          <t>6646878</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>11308</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13514</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>442028</t>
+          <t>442838</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453091</t>
+          <t>453072</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>422887</t>
+          <t>422692</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>870862</t>
+          <t>871140</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>881954</t>
+          <t>882123</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15496</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>13082</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21342</t>
+          <t>22518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>671591</t>
+          <t>671986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>685298</t>
+          <t>685282</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>597291</t>
+          <t>597173</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>608415</t>
+          <t>608358</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1276000</t>
+          <t>1274824</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1291708</t>
+          <t>1291808</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13535</t>
+          <t>13839</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17396</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>675011</t>
+          <t>674686</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>681150</t>
+          <t>681146</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>697315</t>
+          <t>697011</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>707959</t>
+          <t>707916</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1375316</t>
+          <t>1374991</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1387913</t>
+          <t>1388899</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9884</t>
+          <t>10869</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11808</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>609458</t>
+          <t>609415</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>606315</t>
+          <t>605330</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>615131</t>
+          <t>615125</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1219008</t>
+          <t>1218885</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1228735</t>
+          <t>1228698</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13860</t>
+          <t>14188</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17097</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>422073</t>
+          <t>423046</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>433940</t>
+          <t>433612</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>446676</t>
+          <t>445799</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>860132</t>
+          <t>860581</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>874117</t>
+          <t>874162</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>9671</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>243972</t>
+          <t>242795</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>381081</t>
+          <t>380961</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>629070</t>
+          <t>629159</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>637708</t>
+          <t>637705</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>9776</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28163</t>
+          <t>27767</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17003</t>
+          <t>17138</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39836</t>
+          <t>38382</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30317</t>
+          <t>31271</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>58695</t>
+          <t>59397</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3398616</t>
+          <t>3399012</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3417513</t>
+          <t>3417003</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3518473</t>
+          <t>3519927</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3541306</t>
+          <t>3541171</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6926393</t>
+          <t>6925691</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6954771</t>
+          <t>6953817</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>935</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16590</t>
+          <t>15353</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408604</t>
+          <t>407394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418401</t>
+          <t>417999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>386507</t>
+          <t>386747</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394812</t>
+          <t>394820</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>798628</t>
+          <t>799865</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>811347</t>
+          <t>811311</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>848</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>12072</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>582896</t>
+          <t>583562</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>557065</t>
+          <t>555733</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562703</t>
+          <t>562696</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1143398</t>
+          <t>1141968</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1152280</t>
+          <t>1152240</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11177</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13648</t>
+          <t>14408</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>20601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>657920</t>
+          <t>657911</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668199</t>
+          <t>668195</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>647738</t>
+          <t>646978</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>658665</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1311435</t>
+          <t>1309882</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1325110</t>
+          <t>1325659</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11465</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,82 +7735,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3125</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8438</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>8338</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>4032</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>15618</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3125</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8419</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>8338</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>3885</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>15598</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>634583</t>
+          <t>634605</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>644073</t>
+          <t>644085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7853,77 +7853,77 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>99,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>645952</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>640639</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>648076</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,85%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1176</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1286787</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1279507</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1291093</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>98,79%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>99,69%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>645952</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>640658</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>648084</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,7%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,85%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1176</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1286787</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1279527</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1291240</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>98,8%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10953</t>
+          <t>10860</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>471908</t>
+          <t>471082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>486937</t>
+          <t>488035</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>495757</t>
+          <t>495762</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>963814</t>
+          <t>963907</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>973659</t>
+          <t>973650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>905</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7794</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10698</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>13354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>326536</t>
+          <t>326232</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>333435</t>
+          <t>333425</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>367064</t>
+          <t>367398</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>698053</t>
+          <t>698738</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>710148</t>
+          <t>710160</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>252905</t>
+          <t>251913</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>653058</t>
+          <t>653092</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12383</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32105</t>
+          <t>31835</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34501</t>
+          <t>34650</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30556</t>
+          <t>31829</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>58271</t>
+          <t>58698</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3362245</t>
+          <t>3362515</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3381967</t>
+          <t>3381745</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3510041</t>
+          <t>3509892</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3530642</t>
+          <t>3530016</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6880621</t>
+          <t>6880194</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6908336</t>
+          <t>6907063</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18446</t>
+          <t>14829</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19891</t>
+          <t>20352</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>16349</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28641</t>
+          <t>30592</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>418225</t>
+          <t>471611</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>405101</t>
+          <t>462061</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422466</t>
+          <t>475799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>501417</t>
+          <t>490663</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>492202</t>
+          <t>481381</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>507109</t>
+          <t>496233</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>919643</t>
+          <t>962274</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>906999</t>
+          <t>948031</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>926983</t>
+          <t>969453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -10361,12 +10361,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,22 +10386,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15427</t>
+          <t>16153</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,22 +10421,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>10802</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>18087</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -10464,27 +10464,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>536175</t>
+          <t>619653</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535525</t>
+          <t>613874</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10499,27 +10499,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>582846</t>
+          <t>613575</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>576575</t>
+          <t>607040</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>586883</t>
+          <t>617808</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10534,27 +10534,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1119021</t>
+          <t>1233227</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1112524</t>
+          <t>1225942</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1123274</t>
+          <t>1238400</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -10704,12 +10704,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11164</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -10807,27 +10807,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>886576</t>
+          <t>698633</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>881370</t>
+          <t>693114</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>706712</t>
+          <t>729451</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>701717</t>
+          <t>724377</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>709768</t>
+          <t>733435</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1593288</t>
+          <t>1428085</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1587504</t>
+          <t>1421690</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1597252</t>
+          <t>1432593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>14772</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>12376</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>7437</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16274</t>
+          <t>18509</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>17498</t>
+          <t>19439</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11346</t>
+          <t>12837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26200</t>
+          <t>28247</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>554131</t>
+          <t>602282</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>547334</t>
+          <t>594574</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>558271</t>
+          <t>606357</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>537510</t>
+          <t>596479</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>531631</t>
+          <t>590346</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>541597</t>
+          <t>601418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1091641</t>
+          <t>1198763</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1082939</t>
+          <t>1189955</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1097793</t>
+          <t>1205365</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,27 +11380,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>13350</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -11415,67 +11415,67 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>11986</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>6571</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>18328</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>11029</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>5045</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>18694</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -11493,22 +11493,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>361881</t>
+          <t>400149</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>356076</t>
+          <t>393730</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>365166</t>
+          <t>404160</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,67 +11528,67 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>603623</t>
+          <t>434111</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>598683</t>
+          <t>430114</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>607026</t>
+          <t>436781</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>97,94%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>834260</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>827918</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>839675</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>99,22%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>99,78%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1380</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>965504</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>957839</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>971488</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>601</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>7466</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -11836,27 +11836,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>282125</t>
+          <t>309597</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>279128</t>
+          <t>306621</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>423172</t>
+          <t>460881</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>420042</t>
+          <t>457143</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>462899</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>705296</t>
+          <t>770478</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>701570</t>
+          <t>765998</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>707234</t>
+          <t>772989</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32778</t>
+          <t>35185</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>43800</t>
+          <t>49281</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32107</t>
+          <t>38129</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56453</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>64516</t>
+          <t>72324</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49790</t>
+          <t>57944</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>80917</t>
+          <t>89819</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3439101</t>
+          <t>3509719</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3427039</t>
+          <t>3497577</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3447390</t>
+          <t>3518335</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3668480</t>
+          <t>3687673</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3655827</t>
+          <t>3673505</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3680173</t>
+          <t>3698825</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>7107581</t>
+          <t>7197392</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7091180</t>
+          <t>7179897</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7122307</t>
+          <t>7211772</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
